--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ago-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ago-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ago-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ago-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ago-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ago-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1124,7 +1148,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2366-4134-CM25</t>
+          <t>3179-256-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,43 +1173,47 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>22744.91</v>
+        <v>96349.89999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1346279-126-CM25</t>
+          <t>868-159-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,43 +1238,47 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>31574.62</v>
+        <v>6514.24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3179-256-CM25</t>
+          <t>2366-4134-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1271,43 +1303,47 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>96349.89999999999</v>
+        <v>22744.91</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>868-159-CM25</t>
+          <t>1346279-126-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,43 +1368,47 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6514.24</v>
+        <v>31574.62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3179-237-CM25</t>
+          <t>2832-710-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,27 +1433,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.260.400-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1463,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>10838.8</v>
+        <v>19483.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1375761-56-CM25</t>
+          <t>2852-696-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1449,48 +1489,52 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>77.043.435-1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>10151.05</v>
+        <v>14433.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2852-696-CM25</t>
+          <t>3179-237-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1515,43 +1559,47 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.043.435-1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>14433.4</v>
+        <v>10838.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2832-710-CM25</t>
+          <t>1375761-56-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1571,42 +1619,46 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.260.400-8</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>76.465.697-0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>19483.15</v>
+        <v>10151.05</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1712,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1777,11 @@
           <t>76.465.697-0</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1903,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1917,7 +1981,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1385462-115-CM25</t>
+          <t>1469-2229-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,42 +2001,46 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Ortopedic</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.765.630-9</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>25034.25</v>
+        <v>7371.21</v>
       </c>
     </row>
     <row r="26">
@@ -2026,7 +2094,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2220,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2161,7 +2237,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1469-2229-CM25</t>
+          <t>1385462-115-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2181,32 +2257,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>Ortopedic</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>77.765.630-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2292,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>7371.21</v>
+        <v>25034.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2766-900-CM25</t>
+          <t>2421-4235-SE25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,27 +2313,27 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2270,20 +2346,24 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7137.23</v>
+        <v>15557.05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2580-1106-CM25</t>
+          <t>2766-900-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2303,17 +2383,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2331,20 +2411,24 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>17205.2</v>
+        <v>7137.23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>418-2288-CM25</t>
+          <t>2580-1106-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2443,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,43 +2453,47 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>GLOMAX S.A.</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.817.867-4</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>11086.61</v>
+        <v>17205.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2735-1218-CM25</t>
+          <t>418-2288-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2430,27 +2518,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>GLOMAX S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.817.867-4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2548,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>25146.53</v>
+        <v>11086.61</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1079639-744-CM25</t>
+          <t>2735-1218-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2491,43 +2579,47 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>28134.5</v>
+        <v>25146.53</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2343-350-CM25</t>
+          <t>1079639-744-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2634,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,43 +2644,47 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>21404.83</v>
+        <v>28134.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5510-108-CM25</t>
+          <t>2343-350-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2608,17 +2704,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,28 +2724,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>12216.86</v>
+        <v>21404.83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1375158-3-CM25</t>
+          <t>5510-108-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2764,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2774,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.001.000-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO MEDICO LEGAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,28 +2789,32 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>MUEBLES EASTON LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>79.526.830-8</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>379344.16</v>
+        <v>12216.86</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3275-261-CM25</t>
+          <t>1375158-3-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2730,32 +2834,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.001.000-8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.235.755-0</t>
+          <t>79.526.830-8</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2869,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>14119.12</v>
+        <v>379344.16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3275-262-CM25</t>
+          <t>3275-261-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2811,12 +2915,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2930,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>21332.64</v>
+        <v>14119.12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3275-263-CM25</t>
+          <t>3275-262-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2872,28 +2976,32 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.235.755-0</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>18024.74</v>
+        <v>21332.64</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2734-590-CM25</t>
+          <t>3275-263-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2913,32 +3021,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +3056,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>8272.5</v>
+        <v>18024.74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2274-214-CM25</t>
+          <t>2734-590-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,22 +3077,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.253.800-5</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,28 +3102,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA MERCADO PUBLICO SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.559.762-5</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>6703.64</v>
+        <v>8272.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>548875-155-CM25</t>
+          <t>2274-214-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3142,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3152,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>69.253.800-5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>I MUNICIPALIDAD DE LA PINTANA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,28 +3167,32 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIALIZADORA MERCADO PUBLICO SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>76.559.762-5</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>38190.63</v>
+        <v>6703.64</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5178-3868-CM25</t>
+          <t>548875-155-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3101,12 +3217,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,28 +3232,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>9421.719999999999</v>
+        <v>38190.63</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>618-518-CM25</t>
+          <t>5178-3868-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3157,17 +3277,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3297,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>83.732.700-8</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3312,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>6127.4</v>
+        <v>9421.719999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3349-283-CM25</t>
+          <t>618-518-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3218,48 +3338,52 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>13356.61</v>
+        <v>6127.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3710-610-CM25</t>
+          <t>3349-283-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3398,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,43 +3408,47 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.404.809-1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>16249.79</v>
+        <v>13356.61</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2448-694-CM25</t>
+          <t>3710-610-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,7 +3463,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,27 +3473,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.404.809-1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3503,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>23811.37</v>
+        <v>16249.79</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1293138-241-CM25</t>
+          <t>2448-694-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,7 +3524,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,43 +3534,47 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>43160.17</v>
+        <v>23811.37</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>425-581-CM25</t>
+          <t>1293138-241-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3462,17 +3594,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,28 +3614,32 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.235.755-0</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>16532.07</v>
+        <v>43160.17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2704-1496-CM25</t>
+          <t>425-581-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3523,32 +3659,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3694,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>14609.82</v>
+        <v>16532.07</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5251-1407-CM25</t>
+          <t>2704-1496-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3715,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,17 +3725,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>70.729.100-1</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3612,20 +3748,24 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>12024.57</v>
+        <v>14609.82</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>867990-920-CM25</t>
+          <t>5251-1407-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3650,12 +3790,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>70.729.100-1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3673,20 +3813,24 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5948.39</v>
+        <v>12024.57</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1293138-242-CM25</t>
+          <t>867990-920-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3711,12 +3855,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,28 +3870,32 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>MUNDO LOCKERS SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.580.205-9</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>34933.1</v>
+        <v>5948.39</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1293138-243-CM25</t>
+          <t>1293138-242-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3787,12 +3935,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>COMERCIAL VYB SPA</t>
+          <t>MUNDO LOCKERS SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.583.479-1</t>
+          <t>76.580.205-9</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3950,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>32497.27</v>
+        <v>34933.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>765-342-CM25</t>
+          <t>1293138-243-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3833,27 +3981,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO PEDREROS CONCHA</t>
+          <t>COMERCIAL VYB SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>10.595.925-7</t>
+          <t>76.583.479-1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +4011,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>9577.59</v>
+        <v>32497.27</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2176-431-CM25</t>
+          <t>765-342-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,37 +4032,37 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>PEDRO ANTONIO PEDREROS CONCHA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>10.595.925-7</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +4072,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>13466.75</v>
+        <v>9577.59</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3567-533-CM25</t>
+          <t>2176-431-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3955,43 +4103,47 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.150.700-9</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FLORIDA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>13279.81</v>
+        <v>13466.75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1208983-141-CM25</t>
+          <t>3567-533-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4011,48 +4163,52 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.150.700-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>28941.17</v>
+        <v>13279.81</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2173-201-CM25</t>
+          <t>1208983-141-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4072,48 +4228,52 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>22722.3</v>
+        <v>28941.17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1233-110-CM25</t>
+          <t>2173-201-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4133,17 +4293,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.804.010-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4313,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,6 +4328,71 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
+        <v>22722.3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1233-110-CM25</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>60.804.010-2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
         <v>5787.24</v>
       </c>
     </row>
